--- a/outputs/task1_adoption/task1_outputs.xlsx
+++ b/outputs/task1_adoption/task1_outputs.xlsx
@@ -988,7 +988,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Active beta-blocker
-(within 90 days)</t>
+(30-day coverage window)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1013,7 +1013,7 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Active CCB prescription
-(within 90 days)</t>
+(30-day coverage window)</t>
         </is>
       </c>
       <c r="C5" t="n">
